--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/2028-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/2028-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4C7570A9-79B1-4D27-9260-B6F9F55BD345}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{556A6881-7FB3-43B9-9EA0-2AA7B0660589}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{FCA48BD7-6930-4247-B724-BC5B09ADD39F}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{DBF7CAE9-C67B-4D8C-845B-130FC82ED117}"/>
   </bookViews>
   <sheets>
     <sheet name="2028-dividend-20260215_1_2" sheetId="1" r:id="rId1"/>
@@ -1472,30 +1472,30 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7183900C-3452-47FD-AB43-0C6005709FAE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{84DE74A6-4D9D-47B5-8074-BD05489268D5}">
   <dimension ref="A1:X57"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.375" customWidth="1"/>
-    <col min="2" max="2" width="4.875" customWidth="1"/>
-    <col min="3" max="3" width="11" customWidth="1"/>
-    <col min="4" max="4" width="7.125" customWidth="1"/>
-    <col min="5" max="5" width="6.75" customWidth="1"/>
-    <col min="6" max="6" width="7.125" customWidth="1"/>
-    <col min="7" max="8" width="6.75" customWidth="1"/>
-    <col min="9" max="10" width="7.125" customWidth="1"/>
-    <col min="11" max="13" width="6.75" customWidth="1"/>
-    <col min="14" max="15" width="7.125" customWidth="1"/>
-    <col min="16" max="18" width="6.75" customWidth="1"/>
-    <col min="19" max="19" width="7.125" customWidth="1"/>
-    <col min="20" max="20" width="6.75" customWidth="1"/>
-    <col min="21" max="21" width="7.125" customWidth="1"/>
-    <col min="22" max="22" width="6.75" customWidth="1"/>
-    <col min="23" max="23" width="7.125" customWidth="1"/>
-    <col min="24" max="24" width="8.625" customWidth="1"/>
+    <col min="1" max="1" width="3.77734375" customWidth="1"/>
+    <col min="2" max="2" width="4.21875" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" customWidth="1"/>
+    <col min="4" max="4" width="6.109375" customWidth="1"/>
+    <col min="5" max="5" width="5.88671875" customWidth="1"/>
+    <col min="6" max="6" width="6.109375" customWidth="1"/>
+    <col min="7" max="8" width="5.88671875" customWidth="1"/>
+    <col min="9" max="10" width="6.109375" customWidth="1"/>
+    <col min="11" max="13" width="5.88671875" customWidth="1"/>
+    <col min="14" max="15" width="6.109375" customWidth="1"/>
+    <col min="16" max="18" width="5.88671875" customWidth="1"/>
+    <col min="19" max="19" width="6.109375" customWidth="1"/>
+    <col min="20" max="20" width="5.88671875" customWidth="1"/>
+    <col min="21" max="21" width="6.109375" customWidth="1"/>
+    <col min="22" max="22" width="5.88671875" customWidth="1"/>
+    <col min="23" max="23" width="6.109375" customWidth="1"/>
+    <col min="24" max="24" width="6.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
@@ -1529,7 +1529,7 @@
       <c r="W1" s="28"/>
       <c r="X1" s="20"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="21" t="s">
         <v>1</v>
       </c>
@@ -1565,7 +1565,7 @@
       <c r="W2" s="30"/>
       <c r="X2" s="31"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="21" t="s">
         <v>2</v>
       </c>
@@ -1617,7 +1617,7 @@
       </c>
       <c r="X3" s="34"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="23"/>
       <c r="B4" s="24"/>
       <c r="C4" s="7"/>
@@ -1685,7 +1685,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="35">
         <v>2025</v>
       </c>
@@ -1757,7 +1757,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="11" t="s">
         <v>29</v>
       </c>
@@ -1831,7 +1831,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
         <v>29</v>
       </c>
@@ -1905,7 +1905,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="11" t="s">
         <v>29</v>
       </c>
@@ -1979,7 +1979,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="11" t="s">
         <v>29</v>
       </c>
@@ -2053,7 +2053,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="37">
         <v>2024</v>
       </c>
@@ -2125,7 +2125,7 @@
         <v>1.49</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="16" t="s">
         <v>29</v>
       </c>
@@ -2199,7 +2199,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="16" t="s">
         <v>29</v>
       </c>
@@ -2273,7 +2273,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="16" t="s">
         <v>29</v>
       </c>
@@ -2347,7 +2347,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="16" t="s">
         <v>29</v>
       </c>
@@ -2421,7 +2421,7 @@
         <v>1.49</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="16" t="s">
         <v>29</v>
       </c>
@@ -2495,7 +2495,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="35">
         <v>2023</v>
       </c>
@@ -2567,7 +2567,7 @@
         <v>3.78</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="11" t="s">
         <v>29</v>
       </c>
@@ -2641,7 +2641,7 @@
         <v>1.49</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="11" t="s">
         <v>29</v>
       </c>
@@ -2715,7 +2715,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="11" t="s">
         <v>29</v>
       </c>
@@ -2789,7 +2789,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="11" t="s">
         <v>29</v>
       </c>
@@ -2863,7 +2863,7 @@
         <v>2.29</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="11" t="s">
         <v>29</v>
       </c>
@@ -2937,7 +2937,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="37">
         <v>2022</v>
       </c>
@@ -3009,7 +3009,7 @@
         <v>6.24</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="16" t="s">
         <v>29</v>
       </c>
@@ -3083,7 +3083,7 @@
         <v>2.06</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="16" t="s">
         <v>29</v>
       </c>
@@ -3157,7 +3157,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="16" t="s">
         <v>29</v>
       </c>
@@ -3231,7 +3231,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="16" t="s">
         <v>29</v>
       </c>
@@ -3305,7 +3305,7 @@
         <v>4.18</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="35">
         <v>2021</v>
       </c>
@@ -3377,7 +3377,7 @@
         <v>12.3</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="37">
         <v>2020</v>
       </c>
@@ -3449,7 +3449,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="35">
         <v>2019</v>
       </c>
@@ -3521,7 +3521,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="37">
         <v>2018</v>
       </c>
@@ -3593,7 +3593,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="35">
         <v>2017</v>
       </c>
@@ -3665,7 +3665,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="37">
         <v>2016</v>
       </c>
@@ -3737,7 +3737,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="35">
         <v>2015</v>
       </c>
@@ -3809,7 +3809,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="37">
         <v>2014</v>
       </c>
@@ -3881,7 +3881,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="35">
         <v>2013</v>
       </c>
@@ -3953,7 +3953,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="37">
         <v>2012</v>
       </c>
@@ -4025,7 +4025,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="35">
         <v>2011</v>
       </c>
@@ -4097,7 +4097,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="37">
         <v>2010</v>
       </c>
@@ -4169,7 +4169,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="35">
         <v>2009</v>
       </c>
@@ -4241,7 +4241,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A40" s="37">
         <v>2008</v>
       </c>
@@ -4313,7 +4313,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A41" s="35">
         <v>2007</v>
       </c>
@@ -4385,7 +4385,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A42" s="37">
         <v>2006</v>
       </c>
@@ -4457,7 +4457,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A43" s="35">
         <v>2005</v>
       </c>
@@ -4529,7 +4529,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A44" s="37">
         <v>2004</v>
       </c>
@@ -4601,7 +4601,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A45" s="35">
         <v>2003</v>
       </c>
@@ -4673,7 +4673,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A46" s="37">
         <v>2002</v>
       </c>
@@ -4745,7 +4745,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A47" s="35">
         <v>2001</v>
       </c>
@@ -4817,7 +4817,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A48" s="37">
         <v>2000</v>
       </c>
@@ -4889,7 +4889,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A49" s="35">
         <v>1999</v>
       </c>
@@ -4961,7 +4961,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A50" s="37">
         <v>1998</v>
       </c>
@@ -5033,7 +5033,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A51" s="35">
         <v>1997</v>
       </c>
@@ -5105,7 +5105,7 @@
         <v>7.91</v>
       </c>
     </row>
-    <row r="52" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A52" s="37">
         <v>1996</v>
       </c>
@@ -5177,7 +5177,7 @@
         <v>6.76</v>
       </c>
     </row>
-    <row r="53" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A53" s="35">
         <v>1995</v>
       </c>
@@ -5249,7 +5249,7 @@
         <v>4.93</v>
       </c>
     </row>
-    <row r="54" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A54" s="37">
         <v>1994</v>
       </c>
@@ -5321,7 +5321,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="55" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A55" s="35">
         <v>1993</v>
       </c>
@@ -5393,7 +5393,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="56" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A56" s="37">
         <v>1992</v>
       </c>
@@ -5465,7 +5465,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="57" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A57" s="35" t="s">
         <v>45</v>
       </c>
